--- a/data/trans_orig/P1803_2016_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P1803_2016_2023-Habitat-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17794</t>
+          <t>16554</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>36871</t>
+          <t>36873</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16141</t>
+          <t>15339</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>35724</t>
+          <t>35862</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>37526</t>
+          <t>37774</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>64164</t>
+          <t>66343</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,92%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>637929</t>
+          <t>637927</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>657006</t>
+          <t>658246</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -864,7 +864,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>637115</t>
+          <t>636977</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>656698</t>
+          <t>657500</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>94,67%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1283475</t>
+          <t>1281296</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1310113</t>
+          <t>1309865</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,2%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>30848</t>
+          <t>32359</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>58923</t>
+          <t>59771</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,12 +1089,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>35736</t>
+          <t>36332</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>66130</t>
+          <t>63946</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,12 +1124,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>75472</t>
+          <t>74166</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>115839</t>
+          <t>113524</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,5%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>963508</t>
+          <t>962660</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>991583</t>
+          <t>990072</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>94,15%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>976783</t>
+          <t>978967</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1007177</t>
+          <t>1006581</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>93,87%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1949505</t>
+          <t>1951820</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1989872</t>
+          <t>1991178</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,41%</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>17611</t>
+          <t>17404</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>39808</t>
+          <t>39259</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>28405</t>
+          <t>29288</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>53685</t>
+          <t>53849</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>51065</t>
+          <t>49520</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>82869</t>
+          <t>82220</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,12 +1502,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,32%</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>719744</t>
+          <t>720293</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>741941</t>
+          <t>742148</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,12 +1545,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>94,83%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>731326</t>
+          <t>731162</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>756606</t>
+          <t>755723</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,12 +1580,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>93,14%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1461694</t>
+          <t>1462343</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1493498</t>
+          <t>1495043</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,79%</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>45106</t>
+          <t>44707</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>76179</t>
+          <t>76690</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>65701</t>
+          <t>66650</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>102316</t>
+          <t>104731</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>121352</t>
+          <t>120245</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>168026</t>
+          <t>166948</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,43%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>861388</t>
+          <t>860877</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>892461</t>
+          <t>892860</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,87%</t>
+          <t>91,82%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>941463</t>
+          <t>939048</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>978078</t>
+          <t>977129</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,2%</t>
+          <t>89,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1813320</t>
+          <t>1814398</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1859994</t>
+          <t>1861101</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,52%</t>
+          <t>91,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>93,93%</t>
         </is>
       </c>
     </row>
@@ -2103,12 +2103,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>130818</t>
+          <t>132226</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>180874</t>
+          <t>181067</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2118,7 +2118,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>166982</t>
+          <t>169707</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>225840</t>
+          <t>223109</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2153,12 +2153,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>312431</t>
+          <t>315049</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>390129</t>
+          <t>391061</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2188,12 +2188,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,64%</t>
         </is>
       </c>
     </row>
@@ -2216,12 +2216,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3213476</t>
+          <t>3213283</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3263532</t>
+          <t>3262124</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3318702</t>
+          <t>3321433</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3377560</t>
+          <t>3374835</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>93,71%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>95,21%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6548763</t>
+          <t>6547831</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6626461</t>
+          <t>6623843</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2301,12 +2301,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,46%</t>
         </is>
       </c>
     </row>
@@ -2673,32 +2673,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>39773</t>
+          <t>41670</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>28070</t>
+          <t>29008</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>54564</t>
+          <t>56468</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2708,32 +2708,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>57593</t>
+          <t>62764</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>47617</t>
+          <t>51978</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>70864</t>
+          <t>77323</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2743,32 +2743,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>97366</t>
+          <t>104433</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>82196</t>
+          <t>88293</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>114648</t>
+          <t>125321</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,81%</t>
         </is>
       </c>
     </row>
@@ -2786,32 +2786,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>595668</t>
+          <t>649040</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>580877</t>
+          <t>634242</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>607371</t>
+          <t>661702</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,41%</t>
+          <t>91,82%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2821,32 +2821,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>617657</t>
+          <t>669810</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>604386</t>
+          <t>655251</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>627633</t>
+          <t>680596</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>91,43%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,51%</t>
+          <t>89,45%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,95%</t>
+          <t>92,9%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2856,32 +2856,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1213325</t>
+          <t>1318851</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1196043</t>
+          <t>1297963</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1228495</t>
+          <t>1334991</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>92,66%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,25%</t>
+          <t>91,19%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>93,8%</t>
         </is>
       </c>
     </row>
@@ -2899,17 +2899,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2934,17 +2934,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>675250</t>
+          <t>732574</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>675250</t>
+          <t>732574</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>675250</t>
+          <t>732574</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2969,17 +2969,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1310691</t>
+          <t>1423284</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1310691</t>
+          <t>1423284</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1310691</t>
+          <t>1423284</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>312399</t>
+          <t>72460</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>77679</t>
+          <t>54666</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>767311</t>
+          <t>93706</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>26,19%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>64,33%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>86546</t>
+          <t>94108</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>71569</t>
+          <t>78686</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>103242</t>
+          <t>111059</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>398945</t>
+          <t>166568</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>167580</t>
+          <t>141780</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>973546</t>
+          <t>195281</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>45,26%</t>
+          <t>9,21%</t>
         </is>
       </c>
     </row>
@@ -3129,32 +3129,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>880465</t>
+          <t>976457</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>425553</t>
+          <t>955211</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1115185</t>
+          <t>994251</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>73,81%</t>
+          <t>93,09%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>35,67%</t>
+          <t>91,07%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>94,79%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3164,32 +3164,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>871560</t>
+          <t>976730</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>854864</t>
+          <t>959779</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>886537</t>
+          <t>992152</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>90,97%</t>
+          <t>91,21%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,22%</t>
+          <t>89,63%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>92,65%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3199,32 +3199,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1752026</t>
+          <t>1953187</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1177425</t>
+          <t>1924474</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1983391</t>
+          <t>1977975</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>81,45%</t>
+          <t>92,14%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>54,74%</t>
+          <t>90,79%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>93,31%</t>
         </is>
       </c>
     </row>
@@ -3242,17 +3242,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3277,17 +3277,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>958106</t>
+          <t>1070838</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>958106</t>
+          <t>1070838</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>958106</t>
+          <t>1070838</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3312,17 +3312,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2150971</t>
+          <t>2119755</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2150971</t>
+          <t>2119755</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2150971</t>
+          <t>2119755</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3359,32 +3359,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>51101</t>
+          <t>55015</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>37511</t>
+          <t>41449</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>69148</t>
+          <t>73473</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3394,32 +3394,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>72043</t>
+          <t>78591</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>36738</t>
+          <t>66027</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>98856</t>
+          <t>95053</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3429,32 +3429,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>123144</t>
+          <t>133606</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>83800</t>
+          <t>114177</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>151719</t>
+          <t>155745</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,65%</t>
         </is>
       </c>
     </row>
@@ -3472,32 +3472,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>653579</t>
+          <t>748058</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>635532</t>
+          <t>729600</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>667169</t>
+          <t>761624</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>93,15%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,19%</t>
+          <t>90,85%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3507,32 +3507,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>860757</t>
+          <t>733072</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>833944</t>
+          <t>716610</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>896062</t>
+          <t>745636</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>90,32%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,4%</t>
+          <t>88,29%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>91,87%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3542,32 +3542,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1514336</t>
+          <t>1481130</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1485761</t>
+          <t>1458991</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1553680</t>
+          <t>1500559</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>92,48%</t>
+          <t>91,73%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>90,35%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>92,93%</t>
         </is>
       </c>
     </row>
@@ -3585,17 +3585,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3620,17 +3620,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>932800</t>
+          <t>811663</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>932800</t>
+          <t>811663</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>932800</t>
+          <t>811663</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3655,17 +3655,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1637480</t>
+          <t>1614736</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1637480</t>
+          <t>1614736</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1637480</t>
+          <t>1614736</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -3702,32 +3702,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>111235</t>
+          <t>112852</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>92873</t>
+          <t>94596</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>133781</t>
+          <t>136293</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3737,32 +3737,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>129709</t>
+          <t>135344</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>103051</t>
+          <t>117668</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>149502</t>
+          <t>155998</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3772,32 +3772,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>240944</t>
+          <t>248196</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>210469</t>
+          <t>220845</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>271773</t>
+          <t>276653</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,12%</t>
         </is>
       </c>
     </row>
@@ -3815,32 +3815,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>815596</t>
+          <t>877210</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>793050</t>
+          <t>853769</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>833958</t>
+          <t>895466</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>88,0%</t>
+          <t>88,6%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,57%</t>
+          <t>86,23%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,98%</t>
+          <t>90,45%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3850,32 +3850,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>964545</t>
+          <t>983013</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>944752</t>
+          <t>962359</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>991203</t>
+          <t>1000689</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>88,15%</t>
+          <t>87,9%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,34%</t>
+          <t>86,05%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,58%</t>
+          <t>89,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3885,32 +3885,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1780141</t>
+          <t>1860223</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1749312</t>
+          <t>1831766</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1810616</t>
+          <t>1887574</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>88,08%</t>
+          <t>88,23%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,55%</t>
+          <t>86,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,59%</t>
+          <t>89,53%</t>
         </is>
       </c>
     </row>
@@ -3928,17 +3928,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -3963,17 +3963,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1094254</t>
+          <t>1118357</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1094254</t>
+          <t>1118357</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1094254</t>
+          <t>1118357</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3998,17 +3998,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2021085</t>
+          <t>2108419</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2021085</t>
+          <t>2108419</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2021085</t>
+          <t>2108419</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -4045,32 +4045,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>514507</t>
+          <t>281996</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>278006</t>
+          <t>249779</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1172526</t>
+          <t>322394</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>33,89%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4080,32 +4080,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>345891</t>
+          <t>370807</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>283016</t>
+          <t>337119</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>387944</t>
+          <t>401514</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4115,32 +4115,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>860399</t>
+          <t>652803</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>619385</t>
+          <t>610512</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1663521</t>
+          <t>704185</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>9,69%</t>
         </is>
       </c>
     </row>
@@ -4158,32 +4158,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2945310</t>
+          <t>3250766</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2287291</t>
+          <t>3210368</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3181811</t>
+          <t>3282983</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>85,13%</t>
+          <t>92,02%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>66,11%</t>
+          <t>90,87%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4193,32 +4193,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3314519</t>
+          <t>3362624</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3272466</t>
+          <t>3331917</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3377394</t>
+          <t>3396312</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>90,07%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,4%</t>
+          <t>89,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>90,97%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4228,32 +4228,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>6259828</t>
+          <t>6613390</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5456706</t>
+          <t>6562008</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6500842</t>
+          <t>6655681</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>87,92%</t>
+          <t>91,02%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>76,64%</t>
+          <t>90,31%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,3%</t>
+          <t>91,6%</t>
         </is>
       </c>
     </row>
@@ -4271,17 +4271,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4306,17 +4306,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3660410</t>
+          <t>3733431</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3660410</t>
+          <t>3733431</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3660410</t>
+          <t>3733431</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4341,17 +4341,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7120227</t>
+          <t>7266193</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7120227</t>
+          <t>7266193</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7120227</t>
+          <t>7266193</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
